--- a/APIEndpoints.xlsx
+++ b/APIEndpoints.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/38dc1c55ef848d4f/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E190199-CE2E-41A1-9CC6-446562EAEFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{3E190199-CE2E-41A1-9CC6-446562EAEFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF3169AA-1F2B-4B77-9BED-2E18408E9427}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{ED728F8F-AB14-4704-BBEB-5C97877E0192}"/>
   </bookViews>
@@ -51,28 +51,28 @@
     <t>Fetch all available cars.</t>
   </si>
   <si>
-    <t>/api/rent</t>
-  </si>
-  <si>
     <t>POST</t>
   </si>
   <si>
     <t>Create a rental order and save details.</t>
   </si>
   <si>
-    <t>/api/track-order</t>
-  </si>
-  <si>
     <t>Retrieve the status of a rental order by its ID.</t>
   </si>
   <si>
-    <t>/api/checkout</t>
-  </si>
-  <si>
     <t>Process payment using Stripe.</t>
   </si>
   <si>
     <t>/product/cars</t>
+  </si>
+  <si>
+    <t>/order/rent</t>
+  </si>
+  <si>
+    <t>/product/track-order</t>
+  </si>
+  <si>
+    <t>/payment/checkout</t>
   </si>
 </sst>
 </file>
@@ -552,7 +552,7 @@
     </row>
     <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>3</v>
@@ -561,37 +561,37 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>7</v>
-      </c>
     </row>
-    <row r="6" spans="1:3" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
